--- a/report_template.xlsx
+++ b/report_template.xlsx
@@ -534,7 +534,7 @@
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>性能得分=平均(TTFT,速度,E2E 得分)；兼容得分=通过率×100；质量得分=正确率×100；长上下文得分=检索率×100；
-总评分=性能×0.3+兼容×0.3+质量×0.2+长上下文×0.2（权重在评分模型表 L2:M5 可改）。</t>
+总评分=性能×0.3+兼容×0.2+质量×0.3+长上下文×0.2（权重在评分模型表 L2:M5 可改）。</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1413,7 +1413,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>perf_sis_01</t>
+          <t>perf_sis_hf_0124</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
@@ -1465,12 +1465,12 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>perf_sis_02</t>
+          <t>perf_sil_hf_0159</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>短输入短输出</t>
+          <t>短输入长输出</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -1479,37 +1479,37 @@
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>302</v>
+        <v>402</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>362</v>
+        <v>482</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1192</v>
+        <v>10848</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>890</v>
+        <v>10446</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>87</v>
+        <v>1504</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>97.75</v>
+        <v>143.98</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>758</v>
+        <v>632</v>
       </c>
       <c r="K3" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>25.4</v>
+        <v>1160.7</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>8</v>
+        <v>402.6</v>
       </c>
       <c r="O3" s="7" t="n"/>
       <c r="P3" s="7" t="n"/>
@@ -1517,12 +1517,12 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>perf_sis_03</t>
+          <t>perf_lis_hf_0050</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>短输入短输出</t>
+          <t>长输入短输出</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -1531,37 +1531,37 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>297</v>
+        <v>2152</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>356</v>
+        <v>2582</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>723</v>
+        <v>7139</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>426</v>
+        <v>4987</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>126.76</v>
+        <v>15.84</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>717</v>
+        <v>227</v>
       </c>
       <c r="K4" s="8" t="n">
         <v>120</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>47.3</v>
+        <v>249.3</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>27.5</v>
+        <v>164</v>
       </c>
       <c r="O4" s="7" t="n"/>
       <c r="P4" s="7" t="n"/>
@@ -1569,12 +1569,12 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>perf_sil_01</t>
+          <t>perf_lil_hf_0051</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>短输入长输出</t>
+          <t>长输入长输出</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -1583,22 +1583,22 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>716</v>
+        <v>3732</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>859</v>
+        <v>4478</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>21746</v>
+        <v>25746</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>21030</v>
+        <v>22014</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>1125</v>
+        <v>1112</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>53.5</v>
+        <v>50.51</v>
       </c>
       <c r="J5" s="8" t="n">
         <v>659</v>
@@ -1610,10 +1610,10 @@
         <v>25</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>841.2</v>
+        <v>880.6</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>592.8</v>
+        <v>620.6</v>
       </c>
       <c r="O5" s="7" t="n"/>
       <c r="P5" s="7" t="n"/>
@@ -1621,51 +1621,51 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>perf_sil_02</t>
+          <t>perf_sis_hf_0124</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>短输入长输出</t>
+          <t>短输入短输出</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>EasyRouter(示例)</t>
+          <t>Mayi(示例)</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>13231</v>
+        <v>1001</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>12878</v>
+        <v>661</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>1332</v>
+        <v>84</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>103.43</v>
+        <v>127.08</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>548</v>
+        <v>632</v>
       </c>
       <c r="K6" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>757.5</v>
+        <v>26.4</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>308.8</v>
+        <v>10</v>
       </c>
       <c r="O6" s="7" t="n"/>
       <c r="P6" s="7" t="n"/>
@@ -1673,7 +1673,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>perf_sil_03</t>
+          <t>perf_sil_hf_0159</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -1683,41 +1683,41 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>EasyRouter(示例)</t>
+          <t>Mayi(示例)</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>740</v>
+        <v>816</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>888</v>
+        <v>979</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>19029</v>
+        <v>14149</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>18289</v>
+        <v>13333</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>1004</v>
+        <v>994</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>54.9</v>
+        <v>74.55</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>294</v>
+        <v>589</v>
       </c>
       <c r="K7" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>1306.4</v>
+        <v>444.4</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>626.4</v>
+        <v>321.6</v>
       </c>
       <c r="O7" s="7" t="n"/>
       <c r="P7" s="7" t="n"/>
@@ -1725,7 +1725,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>perf_lis_01</t>
+          <t>perf_lis_hf_0050</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -1735,26 +1735,26 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>EasyRouter(示例)</t>
+          <t>Mayi(示例)</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>2608</v>
+        <v>4092</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3130</v>
+        <v>4910</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>7945</v>
+        <v>6216</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>5337</v>
+        <v>2124</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>12.74</v>
+        <v>40.02</v>
       </c>
       <c r="J8" s="8" t="n">
         <v>244</v>
@@ -1766,10 +1766,10 @@
         <v>37</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>144.2</v>
+        <v>57.4</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>81.90000000000001</v>
+        <v>32.6</v>
       </c>
       <c r="O8" s="7" t="n"/>
       <c r="P8" s="7" t="n"/>
@@ -1777,36 +1777,36 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>perf_lis_02</t>
+          <t>perf_lil_hf_0051</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>长输入短输出</t>
+          <t>长输入长输出</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>EasyRouter(示例)</t>
+          <t>Mayi(示例)</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2750</v>
+        <v>3575</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>3300</v>
+        <v>4290</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>3645</v>
+        <v>18782</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>895</v>
+        <v>15207</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>77</v>
+        <v>1282</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>86.03</v>
+        <v>84.3</v>
       </c>
       <c r="J9" s="8" t="n">
         <v>500</v>
@@ -1818,10 +1818,10 @@
         <v>31</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>28.9</v>
+        <v>490.5</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>17</v>
+        <v>288.7</v>
       </c>
       <c r="O9" s="7" t="n"/>
       <c r="P9" s="7" t="n"/>
@@ -1839,858 +1839,26 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>EasyRouter(示例)</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>1484</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>1781</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>3375</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>1891</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>81</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>42.83</v>
-      </c>
-      <c r="J10" s="8" t="n">
-        <v>433</v>
-      </c>
-      <c r="K10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>145.5</v>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>105.9</v>
-      </c>
-      <c r="O10" s="7" t="n"/>
-      <c r="P10" s="7" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>perf_lil_01</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>长输入长输出</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>EasyRouter(示例)</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>1913</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>2296</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>24455</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>22542</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>1142</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>50.66</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>664</v>
-      </c>
-      <c r="K11" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v>727.2</v>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>277.3</v>
-      </c>
-      <c r="O11" s="7" t="n"/>
-      <c r="P11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>perf_lil_02</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>长输入长输出</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>EasyRouter(示例)</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>2955</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>3546</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>18865</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>15910</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>1343</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>84.41</v>
-      </c>
-      <c r="J12" s="8" t="n">
-        <v>473</v>
-      </c>
-      <c r="K12" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="L12" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>1325.8</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>801.5</v>
-      </c>
-      <c r="O12" s="7" t="n"/>
-      <c r="P12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>perf_lil_03</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>长输入长输出</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>EasyRouter(示例)</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>2200</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>2640</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>29502</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>27302</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>1373</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>50.29</v>
-      </c>
-      <c r="J13" s="8" t="n">
-        <v>450</v>
-      </c>
-      <c r="K13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v>737.9</v>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v>361.4</v>
-      </c>
-      <c r="O13" s="7" t="n"/>
-      <c r="P13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>perf_sis_01</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>短输入短输出</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
           <t>Mayi(示例)</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n">
-        <v>810</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>972</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>1985</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>1175</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>84</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>71.48999999999999</v>
-      </c>
-      <c r="J14" s="8" t="n">
-        <v>770</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="O14" s="7" t="n"/>
-      <c r="P14" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>perf_sis_02</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>短输入短输出</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>734</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>881</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>789</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>981.8200000000001</v>
-      </c>
-      <c r="J15" s="8" t="n">
-        <v>232</v>
-      </c>
-      <c r="K15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="M15" s="5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="N15" s="5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O15" s="7" t="n"/>
-      <c r="P15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>perf_sis_03</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>短输入短输出</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>445</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>534</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>1836</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>1391</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>85</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>61.11</v>
-      </c>
-      <c r="J16" s="8" t="n">
-        <v>522</v>
-      </c>
-      <c r="K16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="8" t="n">
-        <v>39</v>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="O16" s="7" t="n"/>
-      <c r="P16" s="7" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>perf_sil_01</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>短输入长输出</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>941</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>1129</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>15481</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>14540</v>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>1171</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>80.54000000000001</v>
-      </c>
-      <c r="J17" s="8" t="n">
-        <v>342</v>
-      </c>
-      <c r="K17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="M17" s="5" t="n">
-        <v>605.8</v>
-      </c>
-      <c r="N17" s="5" t="n">
-        <v>408</v>
-      </c>
-      <c r="O17" s="7" t="n"/>
-      <c r="P17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>perf_sil_02</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>短输入长输出</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>910</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>1092</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>29921</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>29011</v>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>1308</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>45.09</v>
-      </c>
-      <c r="J18" s="8" t="n">
-        <v>570</v>
-      </c>
-      <c r="K18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v>1813.2</v>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v>1005.9</v>
-      </c>
-      <c r="O18" s="7" t="n"/>
-      <c r="P18" s="7" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>perf_sil_03</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>短输入长输出</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>565</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>678</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>12343</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>11778</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>1012</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>85.92</v>
-      </c>
-      <c r="J19" s="8" t="n">
-        <v>356</v>
-      </c>
-      <c r="K19" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="L19" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v>654.3</v>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v>455.4</v>
-      </c>
-      <c r="O19" s="7" t="n"/>
-      <c r="P19" s="7" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>perf_lis_01</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>长输入短输出</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>3349</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>4019</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>8935</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>5586</v>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>62</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="J20" s="8" t="n">
-        <v>594</v>
-      </c>
-      <c r="K20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>151</v>
-      </c>
-      <c r="N20" s="5" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="O20" s="7" t="n"/>
-      <c r="P20" s="7" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>perf_lis_02</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>长输入短输出</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>3886</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>4663</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>4144</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>258</v>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>81</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>313.95</v>
-      </c>
-      <c r="J21" s="8" t="n">
-        <v>317</v>
-      </c>
-      <c r="K21" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="M21" s="5" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="O21" s="7" t="n"/>
-      <c r="P21" s="7" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>perf_lis_03</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>长输入短输出</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>3013</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>3616</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>4963</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>1950</v>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>35.38</v>
-      </c>
-      <c r="J22" s="8" t="n">
-        <v>645</v>
-      </c>
-      <c r="K22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="M22" s="5" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="N22" s="5" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="O22" s="7" t="n"/>
-      <c r="P22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>perf_lil_01</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>长输入长输出</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>4982</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>5978</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>39782</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>34800</v>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>1134</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>32.59</v>
-      </c>
-      <c r="J23" s="8" t="n">
-        <v>712</v>
-      </c>
-      <c r="K23" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="M23" s="5" t="n">
-        <v>870</v>
-      </c>
-      <c r="N23" s="5" t="n">
-        <v>658</v>
-      </c>
-      <c r="O23" s="7" t="n"/>
-      <c r="P23" s="7" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>perf_lil_02</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>长输入长输出</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>4586</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>5503</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>25979</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>21393</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>1327</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>62.03</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>719</v>
-      </c>
-      <c r="K24" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="L24" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v>1069.7</v>
-      </c>
-      <c r="N24" s="5" t="n">
-        <v>402.7</v>
-      </c>
-      <c r="O24" s="7" t="n"/>
-      <c r="P24" s="7" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>perf_lil_03</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>长输入长输出</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>5148</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>6178</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>21493</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>16345</v>
-      </c>
-      <c r="H25" s="8" t="n">
-        <v>1276</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>78.06999999999999</v>
-      </c>
-      <c r="J25" s="8" t="n">
-        <v>743</v>
-      </c>
-      <c r="K25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="M25" s="5" t="n">
-        <v>583.8</v>
-      </c>
-      <c r="N25" s="5" t="n">
-        <v>317.8</v>
-      </c>
-      <c r="O25" s="7" t="n"/>
-      <c r="P25" s="7" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>perf_lis_03</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>长输入短输出</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="6" t="n"/>
-      <c r="J26" s="8" t="n"/>
-      <c r="K26" s="8" t="n"/>
-      <c r="L26" s="8" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="7" t="inlineStr">
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t>timeout</t>
         </is>
       </c>
-      <c r="P26" s="7" t="inlineStr">
+      <c r="P10" s="7" t="inlineStr">
         <is>
           <t>读超时（&gt;180s）</t>
         </is>
@@ -2707,7 +1875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2759,7 +1927,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>cmp_stream_01</t>
+          <t>cmp_stream_hf</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
@@ -2779,19 +1947,19 @@
       </c>
       <c r="E2" s="7" t="n"/>
       <c r="F2" s="8" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="G2" s="7" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>cmp_stream_02</t>
+          <t>cmp_tools_hf</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>stream_sse</t>
+          <t>function_calling</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -2806,19 +1974,19 @@
       </c>
       <c r="E3" s="7" t="n"/>
       <c r="F3" s="8" t="n">
-        <v>205</v>
+        <v>43</v>
       </c>
       <c r="G3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>cmp_stop_01</t>
+          <t>cmp_json_hf</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>stop_param</t>
+          <t>json_mode</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -2833,19 +2001,19 @@
       </c>
       <c r="E4" s="7" t="n"/>
       <c r="F4" s="8" t="n">
-        <v>177</v>
+        <v>136</v>
       </c>
       <c r="G4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>cmp_maxtokens_01</t>
+          <t>cmp_system_hf</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>max_tokens</t>
+          <t>system_prompt</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -2860,19 +2028,19 @@
       </c>
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="8" t="n">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="G5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>cmp_temp0_accept</t>
+          <t>cmp_stop_hf</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>temperature_accept</t>
+          <t>stop_param</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -2887,24 +2055,24 @@
       </c>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="8" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="G6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>cmp_temp0_01</t>
+          <t>cmp_stream_hf</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>temperature_zero</t>
+          <t>stream_sse</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>EasyRouter(示例)</t>
+          <t>Mayi(示例)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -2914,14 +2082,14 @@
       </c>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="8" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>cmp_tools_01</t>
+          <t>cmp_tools_hf</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -2931,7 +2099,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>EasyRouter(示例)</t>
+          <t>Mayi(示例)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -2941,24 +2109,24 @@
       </c>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="8" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="G8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>cmp_tools_02</t>
+          <t>cmp_json_hf</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>function_calling</t>
+          <t>json_mode</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>EasyRouter(示例)</t>
+          <t>Mayi(示例)</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -2968,24 +2136,24 @@
       </c>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="8" t="n">
-        <v>63</v>
+        <v>214</v>
       </c>
       <c r="G9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>cmp_json_01</t>
+          <t>cmp_system_hf</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>json_mode</t>
+          <t>system_prompt</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>EasyRouter(示例)</t>
+          <t>Mayi(示例)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -2995,24 +2163,24 @@
       </c>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="8" t="n">
-        <v>268</v>
+        <v>162</v>
       </c>
       <c r="G10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>cmp_multiturn_01</t>
+          <t>cmp_stop_hf</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>multi_turn</t>
+          <t>stop_param</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>EasyRouter(示例)</t>
+          <t>Mayi(示例)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -3022,341 +2190,9 @@
       </c>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="8" t="n">
-        <v>55</v>
+        <v>252</v>
       </c>
       <c r="G11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>cmp_system_01</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>system_prompt</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>EasyRouter(示例)</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="8" t="n">
-        <v>292</v>
-      </c>
-      <c r="G12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>cmp_stream_01</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>stream_sse</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="8" t="n">
-        <v>84</v>
-      </c>
-      <c r="G13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>cmp_stream_02</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>stream_sse</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="8" t="n">
-        <v>85</v>
-      </c>
-      <c r="G14" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>cmp_stop_01</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>stop_param</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="8" t="n">
-        <v>263</v>
-      </c>
-      <c r="G15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>cmp_maxtokens_01</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>max_tokens</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="8" t="n">
-        <v>104</v>
-      </c>
-      <c r="G16" s="7" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>cmp_temp0_accept</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>temperature_accept</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="8" t="n">
-        <v>155</v>
-      </c>
-      <c r="G17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>cmp_temp0_01</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>temperature_zero</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="8" t="n">
-        <v>290</v>
-      </c>
-      <c r="G18" s="7" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>cmp_tools_01</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>function_calling</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>未返回 tool_calls，模型直接以文本回答</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>236</v>
-      </c>
-      <c r="G19" s="7" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>cmp_tools_02</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>function_calling</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="8" t="n">
-        <v>128</v>
-      </c>
-      <c r="G20" s="7" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>cmp_json_01</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>json_mode</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>输出非 JSON，无法 json.loads</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>296</v>
-      </c>
-      <c r="G21" s="7" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>cmp_multiturn_01</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>multi_turn</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="8" t="n">
-        <v>122</v>
-      </c>
-      <c r="G22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>cmp_system_01</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>system_prompt</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="8" t="n">
-        <v>179</v>
-      </c>
-      <c r="G23" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3369,7 +2205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3427,7 +2263,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>quality_gsm8k_001</t>
+          <t>quality_gsm8k_0037</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
@@ -3452,7 +2288,7 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>"18"</t>
+          <t>"2"</t>
         </is>
       </c>
       <c r="G2" s="7" t="n"/>
@@ -3461,7 +2297,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>quality_gsm8k_002</t>
+          <t>quality_gsm8k_0038</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
@@ -3486,7 +2322,7 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>"3"</t>
+          <t>"10"</t>
         </is>
       </c>
       <c r="G3" s="7" t="n"/>
@@ -3495,7 +2331,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>quality_gsm8k_003</t>
+          <t>quality_gsm8k_0039</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -3520,7 +2356,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>"70000"</t>
+          <t>"18"</t>
         </is>
       </c>
       <c r="G4" s="7" t="n"/>
@@ -3529,7 +2365,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>quality_tqa_001</t>
+          <t>quality_truthfulqa_0035</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -3554,7 +2390,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>["Nothing happens", "the seeds pass through", "digested and pass through"]</t>
+          <t>"B"</t>
         </is>
       </c>
       <c r="G5" s="7" t="n"/>
@@ -3563,7 +2399,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>quality_tqa_002</t>
+          <t>quality_truthfulqa_0036</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -3588,7 +2424,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>["Arctic", "the Arctic", "North Pole"]</t>
+          <t>"B"</t>
         </is>
       </c>
       <c r="G6" s="7" t="n"/>
@@ -3597,7 +2433,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>quality_tqa_003</t>
+          <t>quality_truthfulqa_0037</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -3622,7 +2458,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>["Vatican City", "Vatican"]</t>
+          <t>"B"</t>
         </is>
       </c>
       <c r="G7" s="7" t="n"/>
@@ -3631,32 +2467,32 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>quality_gsm8k_001</t>
+          <t>quality_mmlu_cs_0015</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>math</t>
+          <t>reasoning</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Mayi(示例)</t>
+          <t>EasyRouter(示例)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>judge 未命中</t>
+          <t>judge 命中</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>"18"</t>
+          <t>"A"</t>
         </is>
       </c>
       <c r="G8" s="7" t="n"/>
@@ -3665,17 +2501,17 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>quality_gsm8k_002</t>
+          <t>quality_mmlu_logic_0015</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>math</t>
+          <t>reasoning</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Mayi(示例)</t>
+          <t>EasyRouter(示例)</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -3690,7 +2526,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>"3"</t>
+          <t>"C"</t>
         </is>
       </c>
       <c r="G9" s="7" t="n"/>
@@ -3699,7 +2535,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>quality_gsm8k_003</t>
+          <t>quality_gsm8k_0037</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -3714,17 +2550,17 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>失败</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>judge 命中</t>
+          <t>judge 未命中</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>"70000"</t>
+          <t>"2"</t>
         </is>
       </c>
       <c r="G10" s="7" t="n"/>
@@ -3733,12 +2569,12 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>quality_tqa_001</t>
+          <t>quality_gsm8k_0038</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>hallucination</t>
+          <t>math</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -3758,7 +2594,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>["Nothing happens", "the seeds pass through", "digested and pass through"]</t>
+          <t>"10"</t>
         </is>
       </c>
       <c r="G11" s="7" t="n"/>
@@ -3767,12 +2603,12 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>quality_tqa_002</t>
+          <t>quality_gsm8k_0039</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>hallucination</t>
+          <t>math</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -3782,17 +2618,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>judge 未命中</t>
+          <t>judge 命中</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>["Arctic", "the Arctic", "North Pole"]</t>
+          <t>"18"</t>
         </is>
       </c>
       <c r="G12" s="7" t="n"/>
@@ -3801,7 +2637,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>quality_tqa_003</t>
+          <t>quality_truthfulqa_0035</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -3826,11 +2662,147 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>["Vatican City", "Vatican"]</t>
+          <t>"B"</t>
         </is>
       </c>
       <c r="G13" s="7" t="n"/>
       <c r="H13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>quality_truthfulqa_0036</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>hallucination</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Mayi(示例)</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>judge 未命中</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>"B"</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>quality_truthfulqa_0037</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>hallucination</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Mayi(示例)</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>judge 命中</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>"B"</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>quality_mmlu_cs_0015</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Mayi(示例)</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>judge 命中</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>"A"</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>quality_mmlu_logic_0015</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Mayi(示例)</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>judge 命中</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>"C"</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3843,7 +2815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3918,7 +2890,7 @@
         </is>
       </c>
       <c r="E2" s="6" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -3933,7 +2905,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>lc_needle_32k</t>
+          <t>lc_needle_64k</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
@@ -3942,7 +2914,7 @@
         </is>
       </c>
       <c r="C3" s="8" t="n">
-        <v>32000</v>
+        <v>64000</v>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
@@ -3950,7 +2922,7 @@
         </is>
       </c>
       <c r="E3" s="6" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3965,7 +2937,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>lc_needle_64k</t>
+          <t>lc_needle_128k</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -3974,7 +2946,7 @@
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>64000</v>
+        <v>128000</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -3982,7 +2954,7 @@
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -3997,16 +2969,16 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>lc_needle_128k</t>
+          <t>lc_needle_10k</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>EasyRouter(示例)</t>
+          <t>Mayi(示例)</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>128000</v>
+        <v>10000</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -4014,7 +2986,7 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -4029,7 +3001,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>lc_needle_10k</t>
+          <t>lc_needle_64k</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -4038,30 +3010,34 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>10000</v>
+        <v>64000</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>抽奖码（检索成功）</t>
+          <t>（未命中）</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="H6" s="7" t="n"/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>未检索到</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>lc_needle_32k</t>
+          <t>lc_needle_128k</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -4070,93 +3046,25 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>32000</v>
+        <v>128000</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>跳过</t>
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>抽奖码（检索成功）</t>
+          <t>（未命中）</t>
         </is>
       </c>
       <c r="G7" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="H7" s="7" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>lc_needle_64k</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>64000</v>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>（未命中）</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>未检索到</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>lc_needle_128k</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Mayi(示例)</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>128000</v>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>跳过</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>（未命中）</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>超出标称上下文（64K）</t>
         </is>
@@ -4344,7 +3252,7 @@
         </is>
       </c>
       <c r="M3" s="5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="4">
@@ -4390,7 +3298,7 @@
         </is>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="5">
